--- a/site/exports/hit-shenzhen-robotics.xlsx
+++ b/site/exports/hit-shenzhen-robotics.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rea34220faa2947d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="R174a2404d1a14299"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="R09e3f036c33b4bbc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="Rd20cb2cbb61b4975"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R30508cfddac44478"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Re060f4f3e85142eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="R388be02e70d04ac5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="R135c0902b4584799"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="R8264f0957dce4005"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R64119833fc134d59"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,6 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
+  </x:numFmts>
   <x:fonts count="3">
     <x:font>
       <x:sz val="11"/>
@@ -58,13 +61,21 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="10">
+  <x:cellXfs count="14">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -128,7 +139,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T3_0" displayName="T3_0" ref="A1:G2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T4_0" displayName="T4_0" ref="A1:G2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="校区"/>
@@ -143,7 +154,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T3_1" displayName="T3_1" ref="A1:Q4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T4_1" displayName="T4_1" ref="A1:Q4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="17">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="事件类型"/>
@@ -168,7 +179,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T3_2" displayName="T3_2" ref="A1:J6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T4_2" displayName="T4_2" ref="A1:J6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="导师姓名"/>
@@ -186,7 +197,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T3_3" displayName="T3_3" ref="A1:J3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T4_3" displayName="T4_3" ref="A1:J3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="标题"/>
@@ -204,7 +215,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T3_4" displayName="T3_4" ref="A1:E5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T4_4" displayName="T4_4" ref="A1:E6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="来源ID"/>
@@ -421,55 +432,55 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="9" t="str">
         <x:v>姓名</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="9" t="str">
         <x:v>校区</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="9" t="str">
         <x:v>院系</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="9" t="str">
         <x:v>官方主页</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="9" t="str">
         <x:v>核对日期</x:v>
       </x:c>
-      <x:c r="F1" s="5" t="str">
+      <x:c r="F1" s="9" t="str">
         <x:v>缺项与冲突</x:v>
       </x:c>
-      <x:c r="G1" s="5" t="str">
+      <x:c r="G1" s="9" t="str">
         <x:v>范围</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="64" customHeight="1">
-      <x:c r="A2" s="3" t="str">
-        <x:v>高庆彬</x:v>
-      </x:c>
-      <x:c r="B2" s="3" t="str">
+      <x:c r="A2" s="6" t="str">
+        <x:v>高庆彬</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="str">
         <x:v>深圳</x:v>
       </x:c>
-      <x:c r="C2" s="3" t="str">
+      <x:c r="C2" s="6" t="str">
         <x:v>智能学部/机器人与先进制造学院</x:v>
       </x:c>
-      <x:c r="D2" s="3" t="str">
+      <x:c r="D2" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/gaoqingbin</x:v>
       </x:c>
-      <x:c r="E2" s="3" t="str">
-        <x:v>2026-10-23</x:v>
-      </x:c>
-      <x:c r="F2" s="3" t="str">
+      <x:c r="E2" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F2" s="6" t="str">
         <x:v>样本记录，不代表该院系全体教师；只收录已核实公开信息。；未找到硕士学位信息，不能当作无硕士。；博士主导师当前在职状态存在官方来源时间冲突；指导委员会成员当前任职及简介待核实。；本科导师未知。</x:v>
       </x:c>
-      <x:c r="G2" s="3" t="str">
+      <x:c r="G2" s="6" t="str">
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65fe720dc6484fbf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c2bf3df977246fd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -498,185 +509,185 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="9" t="str">
         <x:v>姓名</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="9" t="str">
         <x:v>事件类型</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="9" t="str">
         <x:v>阶段/职位</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="9" t="str">
         <x:v>机构</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="9" t="str">
         <x:v>开始</x:v>
       </x:c>
-      <x:c r="F1" s="5" t="str">
+      <x:c r="F1" s="9" t="str">
         <x:v>结束</x:v>
       </x:c>
-      <x:c r="G1" s="5" t="str">
+      <x:c r="G1" s="9" t="str">
         <x:v>专业</x:v>
       </x:c>
-      <x:c r="H1" s="5" t="str">
+      <x:c r="H1" s="9" t="str">
         <x:v>国家</x:v>
       </x:c>
-      <x:c r="I1" s="5" t="str">
+      <x:c r="I1" s="9" t="str">
         <x:v>地区</x:v>
       </x:c>
-      <x:c r="J1" s="5" t="str">
+      <x:c r="J1" s="9" t="str">
         <x:v>洲</x:v>
       </x:c>
-      <x:c r="K1" s="5" t="str">
+      <x:c r="K1" s="9" t="str">
         <x:v>历史985分类</x:v>
       </x:c>
-      <x:c r="L1" s="5" t="str">
+      <x:c r="L1" s="9" t="str">
         <x:v>确证授位</x:v>
       </x:c>
-      <x:c r="M1" s="5" t="str">
+      <x:c r="M1" s="9" t="str">
         <x:v>授位日期</x:v>
       </x:c>
-      <x:c r="N1" s="5" t="str">
+      <x:c r="N1" s="9" t="str">
         <x:v>授位来源</x:v>
       </x:c>
-      <x:c r="O1" s="5" t="str">
+      <x:c r="O1" s="9" t="str">
         <x:v>备注及冲突</x:v>
       </x:c>
-      <x:c r="P1" s="5" t="str">
+      <x:c r="P1" s="9" t="str">
         <x:v>地域口径</x:v>
       </x:c>
-      <x:c r="Q1" s="5" t="str">
+      <x:c r="Q1" s="9" t="str">
         <x:v>来源</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="64" customHeight="1">
-      <x:c r="A2" s="3" t="str">
-        <x:v>高庆彬</x:v>
-      </x:c>
-      <x:c r="B2" s="3" t="str">
+      <x:c r="A2" s="6" t="str">
+        <x:v>高庆彬</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="str">
         <x:v>degree</x:v>
       </x:c>
-      <x:c r="C2" s="3" t="str">
+      <x:c r="C2" s="6" t="str">
         <x:v>本科</x:v>
       </x:c>
-      <x:c r="D2" s="3" t="str">
+      <x:c r="D2" s="6" t="str">
         <x:v>哈尔滨工业大学</x:v>
       </x:c>
-      <x:c r="E2" s="3" t="str">
+      <x:c r="E2" s="6" t="str">
         <x:v>2007</x:v>
       </x:c>
-      <x:c r="F2" s="3" t="str">
+      <x:c r="F2" s="6" t="str">
         <x:v>2011</x:v>
       </x:c>
-      <x:c r="G2" s="3" t="str">
+      <x:c r="G2" s="6" t="str">
         <x:v>机械工程</x:v>
       </x:c>
-      <x:c r="H2" s="3" t="str">
+      <x:c r="H2" s="6" t="str">
         <x:v>中国</x:v>
       </x:c>
-      <x:c r="I2" s="3" t="str">
+      <x:c r="I2" s="6" t="str">
         <x:v>中国内地</x:v>
       </x:c>
-      <x:c r="J2" s="3" t="str">
+      <x:c r="J2" s="6" t="str">
         <x:v>亚洲</x:v>
       </x:c>
-      <x:c r="K2" s="3" t="str">
+      <x:c r="K2" s="6" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="L2" s="9" t="b">
+      <x:c r="L2" s="13" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M2" s="3" t="str"/>
-      <x:c r="N2" s="3" t="str"/>
-      <x:c r="O2" s="3" t="str"/>
-      <x:c r="P2" s="3" t="str">
+      <x:c r="M2" s="7" t="str"/>
+      <x:c r="N2" s="6" t="str"/>
+      <x:c r="O2" s="6" t="str"/>
+      <x:c r="P2" s="6" t="str">
         <x:v>院校所在地标准化，不代表个人国籍或全部实际学习地点；中国香港单列，不归为国外。</x:v>
       </x:c>
-      <x:c r="Q2" s="3" t="str">
+      <x:c r="Q2" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/gaoqingbin</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="64" customHeight="1">
-      <x:c r="A3" s="3" t="str">
-        <x:v>高庆彬</x:v>
-      </x:c>
-      <x:c r="B3" s="3" t="str">
+      <x:c r="A3" s="6" t="str">
+        <x:v>高庆彬</x:v>
+      </x:c>
+      <x:c r="B3" s="6" t="str">
         <x:v>degree</x:v>
       </x:c>
-      <x:c r="C3" s="3" t="str">
+      <x:c r="C3" s="6" t="str">
         <x:v>博士</x:v>
       </x:c>
-      <x:c r="D3" s="3" t="str">
+      <x:c r="D3" s="6" t="str">
         <x:v>康涅狄格大学</x:v>
       </x:c>
-      <x:c r="E3" s="3" t="str">
+      <x:c r="E3" s="6" t="str">
         <x:v>2011</x:v>
       </x:c>
-      <x:c r="F3" s="3" t="str">
+      <x:c r="F3" s="6" t="str">
         <x:v>2015</x:v>
       </x:c>
-      <x:c r="G3" s="3" t="str">
+      <x:c r="G3" s="6" t="str">
         <x:v>机械工程</x:v>
       </x:c>
-      <x:c r="H3" s="3" t="str">
+      <x:c r="H3" s="6" t="str">
         <x:v>美国</x:v>
       </x:c>
-      <x:c r="I3" s="3" t="str">
+      <x:c r="I3" s="6" t="str">
         <x:v>美国</x:v>
       </x:c>
-      <x:c r="J3" s="3" t="str">
+      <x:c r="J3" s="6" t="str">
         <x:v>北美洲</x:v>
       </x:c>
-      <x:c r="K3" s="3" t="str">
+      <x:c r="K3" s="6" t="str">
         <x:v>no</x:v>
       </x:c>
-      <x:c r="L3" s="9" t="b">
+      <x:c r="L3" s="13" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M3" s="3" t="str"/>
-      <x:c r="N3" s="3" t="str"/>
-      <x:c r="O3" s="3" t="str"/>
-      <x:c r="P3" s="3" t="str">
+      <x:c r="M3" s="7" t="str"/>
+      <x:c r="N3" s="6" t="str"/>
+      <x:c r="O3" s="6" t="str"/>
+      <x:c r="P3" s="6" t="str">
         <x:v>院校所在地标准化，不代表个人国籍或全部实际学习地点；中国香港单列，不归为国外。</x:v>
       </x:c>
-      <x:c r="Q3" s="3" t="str">
+      <x:c r="Q3" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/gaoqingbin</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="64" customHeight="1">
-      <x:c r="A4" s="3" t="str">
-        <x:v>高庆彬</x:v>
-      </x:c>
-      <x:c r="B4" s="3" t="str">
+      <x:c r="A4" s="6" t="str">
+        <x:v>高庆彬</x:v>
+      </x:c>
+      <x:c r="B4" s="6" t="str">
         <x:v>employment</x:v>
       </x:c>
-      <x:c r="C4" s="3" t="str">
+      <x:c r="C4" s="6" t="str">
         <x:v>副教授、博士生导师</x:v>
       </x:c>
-      <x:c r="D4" s="3" t="str">
+      <x:c r="D4" s="6" t="str">
         <x:v>哈尔滨工业大学</x:v>
       </x:c>
-      <x:c r="E4" s="3" t="str"/>
-      <x:c r="F4" s="3" t="str"/>
-      <x:c r="G4" s="3" t="str"/>
-      <x:c r="H4" s="3" t="str"/>
-      <x:c r="I4" s="3" t="str"/>
-      <x:c r="J4" s="3" t="str"/>
-      <x:c r="K4" s="3" t="str"/>
-      <x:c r="L4" s="3" t="str"/>
-      <x:c r="M4" s="3" t="str"/>
-      <x:c r="N4" s="3" t="str"/>
-      <x:c r="O4" s="3" t="str"/>
-      <x:c r="P4" s="3" t="str"/>
-      <x:c r="Q4" s="3" t="str">
+      <x:c r="E4" s="6" t="str"/>
+      <x:c r="F4" s="6" t="str"/>
+      <x:c r="G4" s="6" t="str"/>
+      <x:c r="H4" s="6" t="str"/>
+      <x:c r="I4" s="6" t="str"/>
+      <x:c r="J4" s="6" t="str"/>
+      <x:c r="K4" s="6" t="str"/>
+      <x:c r="L4" s="6" t="str"/>
+      <x:c r="M4" s="7" t="str"/>
+      <x:c r="N4" s="6" t="str"/>
+      <x:c r="O4" s="6" t="str"/>
+      <x:c r="P4" s="6" t="str"/>
+      <x:c r="Q4" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/gaoqingbin</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf99a4d5acccf425f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85d82a24bcf84349"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -698,175 +709,175 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="9" t="str">
         <x:v>姓名</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="9" t="str">
         <x:v>导师姓名</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="9" t="str">
         <x:v>关系类型</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="9" t="str">
         <x:v>阶段</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="9" t="str">
         <x:v>简介</x:v>
       </x:c>
-      <x:c r="F1" s="5" t="str">
+      <x:c r="F1" s="9" t="str">
         <x:v>在职状态</x:v>
       </x:c>
-      <x:c r="G1" s="5" t="str">
+      <x:c r="G1" s="9" t="str">
         <x:v>状态说明</x:v>
       </x:c>
-      <x:c r="H1" s="5" t="str">
+      <x:c r="H1" s="9" t="str">
         <x:v>已核在职主页</x:v>
       </x:c>
-      <x:c r="I1" s="5" t="str">
+      <x:c r="I1" s="9" t="str">
         <x:v>关系来源</x:v>
       </x:c>
-      <x:c r="J1" s="5" t="str">
+      <x:c r="J1" s="9" t="str">
         <x:v>任职来源</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="64" customHeight="1">
-      <x:c r="A2" s="3" t="str">
-        <x:v>高庆彬</x:v>
-      </x:c>
-      <x:c r="B2" s="3" t="str">
+      <x:c r="A2" s="6" t="str">
+        <x:v>高庆彬</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="str">
         <x:v>Nejat Olgac</x:v>
       </x:c>
-      <x:c r="C2" s="3" t="str">
+      <x:c r="C2" s="6" t="str">
         <x:v>博士主导师</x:v>
       </x:c>
-      <x:c r="D2" s="3" t="str">
+      <x:c r="D2" s="6" t="str">
         <x:v>博士</x:v>
       </x:c>
-      <x:c r="E2" s="3" t="str">
+      <x:c r="E2" s="6" t="str">
         <x:v>康涅狄格大学机械工程学者；学位论文库列为Major Advisor。</x:v>
       </x:c>
-      <x:c r="F2" s="3" t="str">
+      <x:c r="F2" s="6" t="str">
         <x:v>unknown_conflicting</x:v>
       </x:c>
-      <x:c r="G2" s="3" t="str">
+      <x:c r="G2" s="6" t="str">
         <x:v>官方院系页仍列Professor；2026-02-25校董会议人事材料搜索索引列2026-01-01退休，PDF本体访问502，未将退休最终核实，暂不提供在职快捷跳转。</x:v>
       </x:c>
-      <x:c r="H2" s="3" t="str"/>
-      <x:c r="I2" s="3" t="str">
+      <x:c r="H2" s="6" t="str"/>
+      <x:c r="I2" s="6" t="str">
         <x:v>https://digitalcommons.lib.uconn.edu/dissertations/787/</x:v>
       </x:c>
-      <x:c r="J2" s="3" t="str">
+      <x:c r="J2" s="6" t="str">
         <x:v>https://mechanical-aerospace-manufacturing.engineering.uconn.edu/people/faculty/</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="64" customHeight="1">
-      <x:c r="A3" s="3" t="str">
-        <x:v>高庆彬</x:v>
-      </x:c>
-      <x:c r="B3" s="3" t="str">
+      <x:c r="A3" s="6" t="str">
+        <x:v>高庆彬</x:v>
+      </x:c>
+      <x:c r="B3" s="6" t="str">
         <x:v>Jiong Tang</x:v>
       </x:c>
-      <x:c r="C3" s="3" t="str">
+      <x:c r="C3" s="6" t="str">
         <x:v>博士指导委员会成员（Associate Advisor）</x:v>
       </x:c>
-      <x:c r="D3" s="3" t="str">
+      <x:c r="D3" s="6" t="str">
         <x:v>博士</x:v>
       </x:c>
-      <x:c r="E3" s="3" t="str">
+      <x:c r="E3" s="6" t="str">
         <x:v>康涅狄格大学博士指导委员会成员；Associate Advisor不等于博士副导师或共同主导师。</x:v>
       </x:c>
-      <x:c r="F3" s="3" t="str">
+      <x:c r="F3" s="6" t="str">
         <x:v>unknown</x:v>
       </x:c>
-      <x:c r="G3" s="3" t="str"/>
-      <x:c r="H3" s="3" t="str"/>
-      <x:c r="I3" s="3" t="str">
+      <x:c r="G3" s="6" t="str"/>
+      <x:c r="H3" s="6" t="str"/>
+      <x:c r="I3" s="6" t="str">
         <x:v>https://digitalcommons.lib.uconn.edu/dissertations/787/</x:v>
       </x:c>
-      <x:c r="J3" s="3" t="str"/>
+      <x:c r="J3" s="6" t="str"/>
     </x:row>
     <x:row r="4" ht="64" customHeight="1">
-      <x:c r="A4" s="3" t="str">
-        <x:v>高庆彬</x:v>
-      </x:c>
-      <x:c r="B4" s="3" t="str">
+      <x:c r="A4" s="6" t="str">
+        <x:v>高庆彬</x:v>
+      </x:c>
+      <x:c r="B4" s="6" t="str">
         <x:v>Chengyu Cao</x:v>
       </x:c>
-      <x:c r="C4" s="3" t="str">
+      <x:c r="C4" s="6" t="str">
         <x:v>博士指导委员会成员（Associate Advisor）</x:v>
       </x:c>
-      <x:c r="D4" s="3" t="str">
+      <x:c r="D4" s="6" t="str">
         <x:v>博士</x:v>
       </x:c>
-      <x:c r="E4" s="3" t="str">
+      <x:c r="E4" s="6" t="str">
         <x:v>康涅狄格大学博士指导委员会成员；Associate Advisor不等于博士副导师或共同主导师。</x:v>
       </x:c>
-      <x:c r="F4" s="3" t="str">
+      <x:c r="F4" s="6" t="str">
         <x:v>unknown</x:v>
       </x:c>
-      <x:c r="G4" s="3" t="str"/>
-      <x:c r="H4" s="3" t="str"/>
-      <x:c r="I4" s="3" t="str">
+      <x:c r="G4" s="6" t="str"/>
+      <x:c r="H4" s="6" t="str"/>
+      <x:c r="I4" s="6" t="str">
         <x:v>https://digitalcommons.lib.uconn.edu/dissertations/787/</x:v>
       </x:c>
-      <x:c r="J4" s="3" t="str"/>
+      <x:c r="J4" s="6" t="str"/>
     </x:row>
     <x:row r="5" ht="64" customHeight="1">
-      <x:c r="A5" s="3" t="str">
-        <x:v>高庆彬</x:v>
-      </x:c>
-      <x:c r="B5" s="3" t="str">
+      <x:c r="A5" s="6" t="str">
+        <x:v>高庆彬</x:v>
+      </x:c>
+      <x:c r="B5" s="6" t="str">
         <x:v>Bi Zhang</x:v>
       </x:c>
-      <x:c r="C5" s="3" t="str">
+      <x:c r="C5" s="6" t="str">
         <x:v>博士指导委员会成员（Associate Advisor）</x:v>
       </x:c>
-      <x:c r="D5" s="3" t="str">
+      <x:c r="D5" s="6" t="str">
         <x:v>博士</x:v>
       </x:c>
-      <x:c r="E5" s="3" t="str">
+      <x:c r="E5" s="6" t="str">
         <x:v>康涅狄格大学博士指导委员会成员；Associate Advisor不等于博士副导师或共同主导师。</x:v>
       </x:c>
-      <x:c r="F5" s="3" t="str">
+      <x:c r="F5" s="6" t="str">
         <x:v>unknown</x:v>
       </x:c>
-      <x:c r="G5" s="3" t="str"/>
-      <x:c r="H5" s="3" t="str"/>
-      <x:c r="I5" s="3" t="str">
+      <x:c r="G5" s="6" t="str"/>
+      <x:c r="H5" s="6" t="str"/>
+      <x:c r="I5" s="6" t="str">
         <x:v>https://digitalcommons.lib.uconn.edu/dissertations/787/</x:v>
       </x:c>
-      <x:c r="J5" s="3" t="str"/>
+      <x:c r="J5" s="6" t="str"/>
     </x:row>
     <x:row r="6" ht="64" customHeight="1">
-      <x:c r="A6" s="3" t="str">
-        <x:v>高庆彬</x:v>
-      </x:c>
-      <x:c r="B6" s="3" t="str">
+      <x:c r="A6" s="6" t="str">
+        <x:v>高庆彬</x:v>
+      </x:c>
+      <x:c r="B6" s="6" t="str">
         <x:v>Horea Ilies</x:v>
       </x:c>
-      <x:c r="C6" s="3" t="str">
+      <x:c r="C6" s="6" t="str">
         <x:v>博士指导委员会成员（Associate Advisor）</x:v>
       </x:c>
-      <x:c r="D6" s="3" t="str">
+      <x:c r="D6" s="6" t="str">
         <x:v>博士</x:v>
       </x:c>
-      <x:c r="E6" s="3" t="str">
+      <x:c r="E6" s="6" t="str">
         <x:v>康涅狄格大学博士指导委员会成员；Associate Advisor不等于博士副导师或共同主导师。</x:v>
       </x:c>
-      <x:c r="F6" s="3" t="str">
+      <x:c r="F6" s="6" t="str">
         <x:v>unknown</x:v>
       </x:c>
-      <x:c r="G6" s="3" t="str"/>
-      <x:c r="H6" s="3" t="str"/>
-      <x:c r="I6" s="3" t="str">
+      <x:c r="G6" s="6" t="str"/>
+      <x:c r="H6" s="6" t="str"/>
+      <x:c r="I6" s="6" t="str">
         <x:v>https://digitalcommons.lib.uconn.edu/dissertations/787/</x:v>
       </x:c>
-      <x:c r="J6" s="3" t="str"/>
+      <x:c r="J6" s="6" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1613218ae7494325"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R518f688fe4af4e48"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -888,95 +899,95 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="9" t="str">
         <x:v>姓名</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="9" t="str">
         <x:v>标题</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="9" t="str">
         <x:v>年份</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="9" t="str">
         <x:v>DOI</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="9" t="str">
         <x:v>链接</x:v>
       </x:c>
-      <x:c r="F1" s="5" t="str">
+      <x:c r="F1" s="9" t="str">
         <x:v>类型</x:v>
       </x:c>
-      <x:c r="G1" s="5" t="str">
+      <x:c r="G1" s="9" t="str">
         <x:v>收录来源</x:v>
       </x:c>
-      <x:c r="H1" s="5" t="str">
+      <x:c r="H1" s="9" t="str">
         <x:v>作者归属依据</x:v>
       </x:c>
-      <x:c r="I1" s="5" t="str">
+      <x:c r="I1" s="9" t="str">
         <x:v>链接核验范围</x:v>
       </x:c>
-      <x:c r="J1" s="5" t="str">
+      <x:c r="J1" s="9" t="str">
         <x:v>备注</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="64" customHeight="1">
-      <x:c r="A2" s="3" t="str">
-        <x:v>高庆彬</x:v>
-      </x:c>
-      <x:c r="B2" s="3" t="str">
+      <x:c r="A2" s="6" t="str">
+        <x:v>高庆彬</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="str">
         <x:v>Stability Analysis and Novel Control Concepts for Multiple Time-delay Systems</x:v>
       </x:c>
-      <x:c r="C2" s="3" t="n">
+      <x:c r="C2" s="6" t="n">
         <x:v>2015</x:v>
       </x:c>
-      <x:c r="D2" s="3" t="str"/>
-      <x:c r="E2" s="3" t="str">
+      <x:c r="D2" s="6" t="str"/>
+      <x:c r="E2" s="6" t="str">
         <x:v>https://digitalcommons.lib.uconn.edu/dissertations/787/</x:v>
       </x:c>
-      <x:c r="F2" s="3" t="str">
+      <x:c r="F2" s="6" t="str">
         <x:v>doctoral_thesis</x:v>
       </x:c>
-      <x:c r="G2" s="3" t="str">
+      <x:c r="G2" s="6" t="str">
         <x:v>https://digitalcommons.lib.uconn.edu/dissertations/787/</x:v>
       </x:c>
-      <x:c r="H2" s="3" t="str">
+      <x:c r="H2" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/gaoqingbin</x:v>
       </x:c>
-      <x:c r="I2" s="3" t="str"/>
-      <x:c r="J2" s="3" t="str"/>
+      <x:c r="I2" s="6" t="str"/>
+      <x:c r="J2" s="6" t="str"/>
     </x:row>
     <x:row r="3" ht="64" customHeight="1">
-      <x:c r="A3" s="3" t="str">
-        <x:v>高庆彬</x:v>
-      </x:c>
-      <x:c r="B3" s="3" t="str">
+      <x:c r="A3" s="6" t="str">
+        <x:v>高庆彬</x:v>
+      </x:c>
+      <x:c r="B3" s="6" t="str">
         <x:v>Proportional-retarded control of a quasi-zero-stiffness vibration isolator</x:v>
       </x:c>
-      <x:c r="C3" s="3" t="n">
+      <x:c r="C3" s="6" t="n">
         <x:v>2024</x:v>
       </x:c>
-      <x:c r="D3" s="3" t="str">
+      <x:c r="D3" s="6" t="str">
         <x:v>10.1016/j.jsv.2024.118309</x:v>
       </x:c>
-      <x:c r="E3" s="3" t="str">
+      <x:c r="E3" s="6" t="str">
         <x:v>https://doi.org/10.1016/j.jsv.2024.118309</x:v>
       </x:c>
-      <x:c r="F3" s="3" t="str">
+      <x:c r="F3" s="6" t="str">
         <x:v>journal_article</x:v>
       </x:c>
-      <x:c r="G3" s="3" t="str">
+      <x:c r="G3" s="6" t="str">
         <x:v>https://www.sciencedirect.com/science/article/pii/S0022460X24000725</x:v>
       </x:c>
-      <x:c r="H3" s="3" t="str">
+      <x:c r="H3" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/gaoqingbin</x:v>
       </x:c>
-      <x:c r="I3" s="3" t="str"/>
-      <x:c r="J3" s="3" t="str"/>
+      <x:c r="I3" s="6" t="str"/>
+      <x:c r="J3" s="6" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra57fb629d8554e50"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9b5882f207e47ae"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -993,94 +1004,111 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="9" t="str">
         <x:v>姓名</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="9" t="str">
         <x:v>来源ID</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="9" t="str">
         <x:v>链接</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="9" t="str">
         <x:v>核验方式</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="9" t="str">
         <x:v>查阅日期</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="64" customHeight="1">
-      <x:c r="A2" s="3" t="str">
-        <x:v>高庆彬</x:v>
-      </x:c>
-      <x:c r="B2" s="3" t="str">
+      <x:c r="A2" s="6" t="str">
+        <x:v>高庆彬</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="str">
         <x:v>gaoqingbin-official</x:v>
       </x:c>
-      <x:c r="C2" s="3" t="str">
+      <x:c r="C2" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/gaoqingbin</x:v>
       </x:c>
-      <x:c r="D2" s="3" t="str">
+      <x:c r="D2" s="6" t="str">
         <x:v>official_page_public_body_fetched</x:v>
       </x:c>
-      <x:c r="E2" s="3" t="str">
-        <x:v>2026-10-23</x:v>
+      <x:c r="E2" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="64" customHeight="1">
-      <x:c r="A3" s="3" t="str">
-        <x:v>高庆彬</x:v>
-      </x:c>
-      <x:c r="B3" s="3" t="str">
+      <x:c r="A3" s="6" t="str">
+        <x:v>高庆彬</x:v>
+      </x:c>
+      <x:c r="B3" s="6" t="str">
         <x:v>hit-gaoqingbin-publication-1</x:v>
       </x:c>
-      <x:c r="C3" s="3" t="str">
+      <x:c r="C3" s="6" t="str">
         <x:v>https://digitalcommons.lib.uconn.edu/dissertations/787/</x:v>
       </x:c>
-      <x:c r="D3" s="3" t="str">
+      <x:c r="D3" s="6" t="str">
         <x:v>official_publisher_or_institution_metadata</x:v>
       </x:c>
-      <x:c r="E3" s="3" t="str">
-        <x:v>2026-10-23</x:v>
+      <x:c r="E3" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="64" customHeight="1">
-      <x:c r="A4" s="3" t="str">
-        <x:v>高庆彬</x:v>
-      </x:c>
-      <x:c r="B4" s="3" t="str">
+      <x:c r="A4" s="6" t="str">
+        <x:v>高庆彬</x:v>
+      </x:c>
+      <x:c r="B4" s="6" t="str">
         <x:v>hit-gaoqingbin-publication-2</x:v>
       </x:c>
-      <x:c r="C4" s="3" t="str">
+      <x:c r="C4" s="6" t="str">
         <x:v>https://www.sciencedirect.com/science/article/pii/S0022460X24000725</x:v>
       </x:c>
-      <x:c r="D4" s="3" t="str">
+      <x:c r="D4" s="6" t="str">
         <x:v>official_publisher_or_institution_metadata</x:v>
       </x:c>
-      <x:c r="E4" s="3" t="str">
-        <x:v>2026-10-23</x:v>
+      <x:c r="E4" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="64" customHeight="1">
-      <x:c r="A5" s="3" t="str">
-        <x:v>高庆彬</x:v>
-      </x:c>
-      <x:c r="B5" s="3" t="str">
+      <x:c r="A5" s="6" t="str">
+        <x:v>高庆彬</x:v>
+      </x:c>
+      <x:c r="B5" s="6" t="str">
         <x:v>uconn-advisory-committee-definition</x:v>
       </x:c>
-      <x:c r="C5" s="3" t="str">
+      <x:c r="C5" s="6" t="str">
         <x:v>https://grad.uconn.edu/wp-content/uploads/sites/2114/2021/02/Meeting-Minutes-Summary-GFC-10.28.2020-Revised-and-Approved.pdf</x:v>
       </x:c>
-      <x:c r="D5" s="3" t="str">
+      <x:c r="D5" s="6" t="str">
         <x:v>parent_independently_verified_official_policy</x:v>
       </x:c>
-      <x:c r="E5" s="3" t="str">
-        <x:v>2026-10-23</x:v>
+      <x:c r="E5" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="64" customHeight="1">
+      <x:c r="A6" s="6" t="str">
+        <x:v>高庆彬</x:v>
+      </x:c>
+      <x:c r="B6" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C6" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D6" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E6" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3e02abfdaea4836"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f5ce049958045ef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/exports/hit-shenzhen-robotics.xlsx
+++ b/site/exports/hit-shenzhen-robotics.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Re060f4f3e85142eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="R388be02e70d04ac5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="R135c0902b4584799"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="R8264f0957dce4005"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R64119833fc134d59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R1a724107abc241c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="Raded4db7140a4901"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="Rf773777605ad493f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="R29f74ab6685346f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="Ra8c841f514d94f1c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,8 +139,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T4_0" displayName="T4_0" ref="A1:G2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="7">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T4_0" displayName="T4_0" ref="A1:I2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="9">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="校区"/>
     <x:tableColumn id="3" name="院系"/>
@@ -148,6 +148,8 @@
     <x:tableColumn id="5" name="核对日期"/>
     <x:tableColumn id="6" name="缺项与冲突"/>
     <x:tableColumn id="7" name="范围"/>
+    <x:tableColumn id="8" name="主页可用性"/>
+    <x:tableColumn id="9" name="替代官方职业报道（非个人主页）"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -429,6 +431,8 @@
     <x:col min="5" max="5" width="26" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="55" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="55" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="26" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="26" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -453,6 +457,12 @@
       <x:c r="G1" s="9" t="str">
         <x:v>范围</x:v>
       </x:c>
+      <x:c r="H1" s="9" t="str">
+        <x:v>主页可用性</x:v>
+      </x:c>
+      <x:c r="I1" s="9" t="str">
+        <x:v>替代官方职业报道（非个人主页）</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="64" customHeight="1">
       <x:c r="A2" s="6" t="str">
@@ -476,11 +486,15 @@
       <x:c r="G2" s="6" t="str">
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
+      <x:c r="H2" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I2" s="6" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c2bf3df977246fd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd03e4e071e1941e2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -687,7 +701,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85d82a24bcf84349"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4af36f2022b6431c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -877,7 +891,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R518f688fe4af4e48"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R315c5fd9048844a5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -987,7 +1001,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9b5882f207e47ae"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref264996e4b940c9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1108,7 +1122,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f5ce049958045ef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2f05b18205346f7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/exports/hit-shenzhen-robotics.xlsx
+++ b/site/exports/hit-shenzhen-robotics.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R1a724107abc241c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="Raded4db7140a4901"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="Rf773777605ad493f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="R29f74ab6685346f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="Ra8c841f514d94f1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R9469cd03f4bc4cb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="Rc210032b087e4b11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="R9dec00998672455c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="Ra7c707af9ad04d12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R22ae921c9dc3481d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,8 +139,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T4_0" displayName="T4_0" ref="A1:I2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="9">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T4_0" displayName="T4_0" ref="A1:K2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="11">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="校区"/>
     <x:tableColumn id="3" name="院系"/>
@@ -150,14 +150,16 @@
     <x:tableColumn id="7" name="范围"/>
     <x:tableColumn id="8" name="主页可用性"/>
     <x:tableColumn id="9" name="替代官方职业报道（非个人主页）"/>
+    <x:tableColumn id="10" name="所属学校ID"/>
+    <x:tableColumn id="11" name="所属学校"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T4_1" displayName="T4_1" ref="A1:Q4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="17">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T4_1" displayName="T4_1" ref="A1:S4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="19">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="事件类型"/>
     <x:tableColumn id="3" name="阶段/职位"/>
@@ -175,14 +177,16 @@
     <x:tableColumn id="15" name="备注及冲突"/>
     <x:tableColumn id="16" name="地域口径"/>
     <x:tableColumn id="17" name="来源"/>
+    <x:tableColumn id="18" name="所属学校ID"/>
+    <x:tableColumn id="19" name="所属学校"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T4_2" displayName="T4_2" ref="A1:J6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="10">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T4_2" displayName="T4_2" ref="A1:L6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="12">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="导师姓名"/>
     <x:tableColumn id="3" name="关系类型"/>
@@ -193,14 +197,16 @@
     <x:tableColumn id="8" name="已核在职主页"/>
     <x:tableColumn id="9" name="关系来源"/>
     <x:tableColumn id="10" name="任职来源"/>
+    <x:tableColumn id="11" name="所属学校ID"/>
+    <x:tableColumn id="12" name="所属学校"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T4_3" displayName="T4_3" ref="A1:J3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="10">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T4_3" displayName="T4_3" ref="A1:L3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="12">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="标题"/>
     <x:tableColumn id="3" name="年份"/>
@@ -211,19 +217,23 @@
     <x:tableColumn id="8" name="作者归属依据"/>
     <x:tableColumn id="9" name="链接核验范围"/>
     <x:tableColumn id="10" name="备注"/>
+    <x:tableColumn id="11" name="所属学校ID"/>
+    <x:tableColumn id="12" name="所属学校"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T4_4" displayName="T4_4" ref="A1:E6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="5">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T4_4" displayName="T4_4" ref="A1:G6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="7">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="来源ID"/>
     <x:tableColumn id="3" name="链接"/>
     <x:tableColumn id="4" name="核验方式"/>
     <x:tableColumn id="5" name="查阅日期"/>
+    <x:tableColumn id="6" name="所属学校ID"/>
+    <x:tableColumn id="7" name="所属学校"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -433,6 +443,8 @@
     <x:col min="7" max="7" width="55" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="26" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="26" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="26" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="26" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -463,6 +475,12 @@
       <x:c r="I1" s="9" t="str">
         <x:v>替代官方职业报道（非个人主页）</x:v>
       </x:c>
+      <x:c r="J1" s="9" t="str">
+        <x:v>所属学校ID</x:v>
+      </x:c>
+      <x:c r="K1" s="9" t="str">
+        <x:v>所属学校</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="64" customHeight="1">
       <x:c r="A2" s="6" t="str">
@@ -490,11 +508,17 @@
         <x:v>公开个人页（时效以核对日为准）</x:v>
       </x:c>
       <x:c r="I2" s="6" t="str"/>
+      <x:c r="J2" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="K2" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd03e4e071e1941e2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd552424674404e82"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -520,6 +544,8 @@
     <x:col min="15" max="15" width="55" hidden="0" customWidth="1"/>
     <x:col min="16" max="16" width="26" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="55" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="26" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="26" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -574,6 +600,12 @@
       <x:c r="Q1" s="9" t="str">
         <x:v>来源</x:v>
       </x:c>
+      <x:c r="R1" s="9" t="str">
+        <x:v>所属学校ID</x:v>
+      </x:c>
+      <x:c r="S1" s="9" t="str">
+        <x:v>所属学校</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="64" customHeight="1">
       <x:c r="A2" s="6" t="str">
@@ -621,6 +653,12 @@
       <x:c r="Q2" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/gaoqingbin</x:v>
       </x:c>
+      <x:c r="R2" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S2" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="64" customHeight="1">
       <x:c r="A3" s="6" t="str">
@@ -667,6 +705,12 @@
       </x:c>
       <x:c r="Q3" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/gaoqingbin</x:v>
+      </x:c>
+      <x:c r="R3" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S3" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="64" customHeight="1">
@@ -697,11 +741,17 @@
       <x:c r="Q4" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/gaoqingbin</x:v>
       </x:c>
+      <x:c r="R4" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S4" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4af36f2022b6431c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R69ac8309166d4e36"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -720,6 +770,8 @@
     <x:col min="8" max="8" width="26" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="55" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="55" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="26" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="26" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -753,6 +805,12 @@
       <x:c r="J1" s="9" t="str">
         <x:v>任职来源</x:v>
       </x:c>
+      <x:c r="K1" s="9" t="str">
+        <x:v>所属学校ID</x:v>
+      </x:c>
+      <x:c r="L1" s="9" t="str">
+        <x:v>所属学校</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="64" customHeight="1">
       <x:c r="A2" s="6" t="str">
@@ -782,6 +840,12 @@
       </x:c>
       <x:c r="J2" s="6" t="str">
         <x:v>https://mechanical-aerospace-manufacturing.engineering.uconn.edu/people/faculty/</x:v>
+      </x:c>
+      <x:c r="K2" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L2" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="64" customHeight="1">
@@ -809,6 +873,12 @@
         <x:v>https://digitalcommons.lib.uconn.edu/dissertations/787/</x:v>
       </x:c>
       <x:c r="J3" s="6" t="str"/>
+      <x:c r="K3" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L3" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="64" customHeight="1">
       <x:c r="A4" s="6" t="str">
@@ -835,6 +905,12 @@
         <x:v>https://digitalcommons.lib.uconn.edu/dissertations/787/</x:v>
       </x:c>
       <x:c r="J4" s="6" t="str"/>
+      <x:c r="K4" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L4" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="64" customHeight="1">
       <x:c r="A5" s="6" t="str">
@@ -861,6 +937,12 @@
         <x:v>https://digitalcommons.lib.uconn.edu/dissertations/787/</x:v>
       </x:c>
       <x:c r="J5" s="6" t="str"/>
+      <x:c r="K5" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L5" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="64" customHeight="1">
       <x:c r="A6" s="6" t="str">
@@ -887,11 +969,17 @@
         <x:v>https://digitalcommons.lib.uconn.edu/dissertations/787/</x:v>
       </x:c>
       <x:c r="J6" s="6" t="str"/>
+      <x:c r="K6" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L6" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R315c5fd9048844a5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44628eba918a4f67"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -910,6 +998,8 @@
     <x:col min="8" max="8" width="26" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="55" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="55" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="26" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="26" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -943,6 +1033,12 @@
       <x:c r="J1" s="9" t="str">
         <x:v>备注</x:v>
       </x:c>
+      <x:c r="K1" s="9" t="str">
+        <x:v>所属学校ID</x:v>
+      </x:c>
+      <x:c r="L1" s="9" t="str">
+        <x:v>所属学校</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="64" customHeight="1">
       <x:c r="A2" s="6" t="str">
@@ -969,6 +1065,12 @@
       </x:c>
       <x:c r="I2" s="6" t="str"/>
       <x:c r="J2" s="6" t="str"/>
+      <x:c r="K2" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L2" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="64" customHeight="1">
       <x:c r="A3" s="6" t="str">
@@ -997,11 +1099,17 @@
       </x:c>
       <x:c r="I3" s="6" t="str"/>
       <x:c r="J3" s="6" t="str"/>
+      <x:c r="K3" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L3" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref264996e4b940c9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7d4db702e84408a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1015,6 +1123,8 @@
     <x:col min="3" max="3" width="55" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="26" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="26" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="26" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="26" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -1033,6 +1143,12 @@
       <x:c r="E1" s="9" t="str">
         <x:v>查阅日期</x:v>
       </x:c>
+      <x:c r="F1" s="9" t="str">
+        <x:v>所属学校ID</x:v>
+      </x:c>
+      <x:c r="G1" s="9" t="str">
+        <x:v>所属学校</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="64" customHeight="1">
       <x:c r="A2" s="6" t="str">
@@ -1050,6 +1166,12 @@
       <x:c r="E2" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F2" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G2" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="64" customHeight="1">
       <x:c r="A3" s="6" t="str">
@@ -1067,6 +1189,12 @@
       <x:c r="E3" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F3" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G3" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="64" customHeight="1">
       <x:c r="A4" s="6" t="str">
@@ -1084,6 +1212,12 @@
       <x:c r="E4" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F4" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G4" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="64" customHeight="1">
       <x:c r="A5" s="6" t="str">
@@ -1101,6 +1235,12 @@
       <x:c r="E5" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F5" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G5" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="64" customHeight="1">
       <x:c r="A6" s="6" t="str">
@@ -1117,12 +1257,18 @@
       </x:c>
       <x:c r="E6" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F6" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G6" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2f05b18205346f7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R850903b496604736"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/exports/hit-shenzhen-robotics.xlsx
+++ b/site/exports/hit-shenzhen-robotics.xlsx
@@ -452,8 +452,8 @@
     <col width="53.2" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
-    <col width="18.2" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="37.8" customWidth="1" min="7" max="7"/>
+    <col width="26.6" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
@@ -482,7 +482,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>核对日期</t>
+          <t>已记录来源检索日期</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -549,12 +549,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
